--- a/FILTER.xlsx
+++ b/FILTER.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOFTWARE\GIT HUB\pdf-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FAA2258-B0B6-4DCD-97DC-FDD74B410679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3369EAE3-C74A-4A87-A1B7-EE115F87CF59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="283">
   <si>
     <t>NXT II</t>
   </si>
@@ -882,6 +882,9 @@
   </si>
   <si>
     <t>NXT III;NXT II;NXT IIc;NXT</t>
+  </si>
+  <si>
+    <t>NXTR_S;NXTR_A;AIMEXR;NXT_III;NXT_IIIc;AIMEX_III;AIMEX_IIIc;</t>
   </si>
 </sst>
 </file>
@@ -1228,7 +1231,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:O145"/>
+  <dimension ref="A1:O146"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
@@ -3106,6 +3109,9 @@
       </c>
     </row>
     <row r="68" spans="9:14" x14ac:dyDescent="0.3">
+      <c r="I68" t="s">
+        <v>282</v>
+      </c>
       <c r="L68" t="s">
         <v>71</v>
       </c>
@@ -3538,6 +3544,9 @@
       </c>
     </row>
     <row r="122" spans="12:14" x14ac:dyDescent="0.3">
+      <c r="L122" t="s">
+        <v>282</v>
+      </c>
       <c r="N122" t="s">
         <v>262</v>
       </c>
@@ -3655,6 +3664,11 @@
     <row r="145" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N145" t="s">
         <v>239</v>
+      </c>
+    </row>
+    <row r="146" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N146" t="s">
+        <v>282</v>
       </c>
     </row>
   </sheetData>
